--- a/sample-data/EAC_Attendance_4_Cycles.xlsx
+++ b/sample-data/EAC_Attendance_4_Cycles.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1381"/>
+  <dimension ref="A1:L1511"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1164,21 +1164,13 @@
           <t>02/01/2026</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>VL</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1308,7 +1300,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1408,7 +1400,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3132,7 +3124,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3182,7 +3174,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3429,10 +3421,14 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr"/>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
@@ -4255,14 +4251,10 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>16:40</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr">
         <is>
@@ -4504,7 +4496,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -5691,10 +5683,14 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr"/>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr">
         <is>
@@ -5786,7 +5782,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -5836,7 +5832,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -6028,7 +6024,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -6078,7 +6074,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -7104,7 +7100,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -8034,7 +8030,7 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -9024,7 +9020,7 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -10005,14 +10001,10 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>16:40</t>
-        </is>
-      </c>
-      <c r="H204" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr"/>
       <c r="I204" t="inlineStr"/>
       <c r="J204" t="inlineStr">
         <is>
@@ -10201,10 +10193,14 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H208" t="inlineStr"/>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="I208" t="inlineStr"/>
       <c r="J208" t="inlineStr">
         <is>
@@ -11173,14 +11169,10 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>16:40</t>
-        </is>
-      </c>
-      <c r="H228" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr"/>
       <c r="I228" t="inlineStr"/>
       <c r="J228" t="inlineStr">
         <is>
@@ -12412,7 +12404,7 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
@@ -13143,14 +13135,10 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>16:40</t>
-        </is>
-      </c>
-      <c r="H271" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr"/>
       <c r="I271" t="inlineStr"/>
       <c r="J271" t="inlineStr">
         <is>
@@ -13826,7 +13814,7 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
@@ -14123,10 +14111,14 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H291" t="inlineStr"/>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="I291" t="inlineStr"/>
       <c r="J291" t="inlineStr">
         <is>
@@ -14510,7 +14502,7 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
@@ -15550,7 +15542,7 @@
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
@@ -16134,7 +16126,7 @@
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
@@ -16339,14 +16331,10 @@
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>16:40</t>
-        </is>
-      </c>
-      <c r="H339" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr"/>
       <c r="I339" t="inlineStr"/>
       <c r="J339" t="inlineStr">
         <is>
@@ -16627,14 +16615,10 @@
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>16:40</t>
-        </is>
-      </c>
-      <c r="H345" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr"/>
       <c r="I345" t="inlineStr"/>
       <c r="J345" t="inlineStr">
         <is>
@@ -16818,7 +16802,7 @@
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
@@ -16968,7 +16952,7 @@
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
@@ -17406,7 +17390,7 @@
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
@@ -17798,7 +17782,7 @@
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="G369" t="inlineStr">
@@ -19280,7 +19264,7 @@
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="G402" t="inlineStr">
@@ -19514,7 +19498,7 @@
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="G407" t="inlineStr">
@@ -19710,7 +19694,7 @@
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="G411" t="inlineStr">
@@ -19760,7 +19744,7 @@
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="G412" t="inlineStr">
@@ -20778,7 +20762,7 @@
       </c>
       <c r="F433" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="G433" t="inlineStr">
@@ -21070,7 +21054,7 @@
       </c>
       <c r="F439" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="G439" t="inlineStr">
@@ -21125,14 +21109,10 @@
       </c>
       <c r="G440" t="inlineStr">
         <is>
-          <t>16:40</t>
-        </is>
-      </c>
-      <c r="H440" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H440" t="inlineStr"/>
       <c r="I440" t="inlineStr"/>
       <c r="J440" t="inlineStr">
         <is>
@@ -22164,7 +22144,7 @@
       </c>
       <c r="F464" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="G464" t="inlineStr">
@@ -22456,7 +22436,7 @@
       </c>
       <c r="F470" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="G470" t="inlineStr">
@@ -22511,14 +22491,10 @@
       </c>
       <c r="G471" t="inlineStr">
         <is>
-          <t>16:40</t>
-        </is>
-      </c>
-      <c r="H471" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H471" t="inlineStr"/>
       <c r="I471" t="inlineStr"/>
       <c r="J471" t="inlineStr">
         <is>
@@ -22807,14 +22783,10 @@
       </c>
       <c r="G477" t="inlineStr">
         <is>
-          <t>16:40</t>
-        </is>
-      </c>
-      <c r="H477" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H477" t="inlineStr"/>
       <c r="I477" t="inlineStr"/>
       <c r="J477" t="inlineStr">
         <is>
@@ -25410,7 +25382,7 @@
       </c>
       <c r="F533" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="G533" t="inlineStr">
@@ -25515,14 +25487,10 @@
       </c>
       <c r="G535" t="inlineStr">
         <is>
-          <t>16:40</t>
-        </is>
-      </c>
-      <c r="H535" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="H535" t="inlineStr"/>
       <c r="I535" t="inlineStr"/>
       <c r="J535" t="inlineStr">
         <is>
@@ -25756,7 +25724,7 @@
       </c>
       <c r="F540" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="G540" t="inlineStr">
@@ -25998,7 +25966,7 @@
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="G545" t="inlineStr">
@@ -26153,10 +26121,14 @@
       </c>
       <c r="G548" t="inlineStr">
         <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H548" t="inlineStr"/>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="H548" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="I548" t="inlineStr"/>
       <c r="J548" t="inlineStr">
         <is>
@@ -26198,7 +26170,7 @@
       </c>
       <c r="F549" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="G549" t="inlineStr">
@@ -27608,7 +27580,7 @@
       </c>
       <c r="F578" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="G578" t="inlineStr">
@@ -28648,7 +28620,7 @@
       </c>
       <c r="F602" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="G602" t="inlineStr">
@@ -29633,10 +29605,14 @@
       </c>
       <c r="G622" t="inlineStr">
         <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H622" t="inlineStr"/>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="H622" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="I622" t="inlineStr"/>
       <c r="J622" t="inlineStr">
         <is>
@@ -30125,10 +30101,14 @@
       </c>
       <c r="G632" t="inlineStr">
         <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H632" t="inlineStr"/>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="H632" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="I632" t="inlineStr"/>
       <c r="J632" t="inlineStr">
         <is>
@@ -30267,10 +30247,14 @@
       </c>
       <c r="G635" t="inlineStr">
         <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="H635" t="inlineStr"/>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="H635" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="I635" t="inlineStr"/>
       <c r="J635" t="inlineStr">
         <is>
@@ -30809,10 +30793,14 @@
       </c>
       <c r="G646" t="inlineStr">
         <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H646" t="inlineStr"/>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="H646" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="I646" t="inlineStr"/>
       <c r="J646" t="inlineStr">
         <is>
@@ -30996,7 +30984,7 @@
       </c>
       <c r="F650" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="G650" t="inlineStr">
@@ -32674,7 +32662,7 @@
       </c>
       <c r="F687" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="G687" t="inlineStr">
@@ -32724,7 +32712,7 @@
       </c>
       <c r="F688" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="G688" t="inlineStr">
@@ -33892,7 +33880,7 @@
       </c>
       <c r="F712" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="G712" t="inlineStr">
@@ -34334,7 +34322,7 @@
       </c>
       <c r="F721" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="G721" t="inlineStr">
@@ -35224,7 +35212,7 @@
       </c>
       <c r="F742" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="G742" t="inlineStr">
@@ -36927,10 +36915,14 @@
       </c>
       <c r="G777" t="inlineStr">
         <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H777" t="inlineStr"/>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="H777" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="I777" t="inlineStr"/>
       <c r="J777" t="inlineStr">
         <is>
@@ -37114,7 +37106,7 @@
       </c>
       <c r="F781" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="G781" t="inlineStr">
@@ -37169,10 +37161,14 @@
       </c>
       <c r="G782" t="inlineStr">
         <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H782" t="inlineStr"/>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="H782" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="I782" t="inlineStr"/>
       <c r="J782" t="inlineStr">
         <is>
@@ -37369,14 +37365,10 @@
       </c>
       <c r="G786" t="inlineStr">
         <is>
-          <t>16:40</t>
-        </is>
-      </c>
-      <c r="H786" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H786" t="inlineStr"/>
       <c r="I786" t="inlineStr"/>
       <c r="J786" t="inlineStr">
         <is>
@@ -37610,7 +37602,7 @@
       </c>
       <c r="F791" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="G791" t="inlineStr">
@@ -38797,10 +38789,14 @@
       </c>
       <c r="G818" t="inlineStr">
         <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H818" t="inlineStr"/>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="H818" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="I818" t="inlineStr"/>
       <c r="J818" t="inlineStr">
         <is>
@@ -38892,7 +38888,7 @@
       </c>
       <c r="F820" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="G820" t="inlineStr">
@@ -39864,7 +39860,7 @@
       </c>
       <c r="F840" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="G840" t="inlineStr">
@@ -40790,7 +40786,7 @@
       </c>
       <c r="F859" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="G859" t="inlineStr">
@@ -40840,7 +40836,7 @@
       </c>
       <c r="F860" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="G860" t="inlineStr">
@@ -41885,10 +41881,14 @@
       </c>
       <c r="G884" t="inlineStr">
         <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H884" t="inlineStr"/>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="H884" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="I884" t="inlineStr"/>
       <c r="J884" t="inlineStr">
         <is>
@@ -41930,7 +41930,7 @@
       </c>
       <c r="F885" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="G885" t="inlineStr">
@@ -42756,7 +42756,7 @@
       </c>
       <c r="F902" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="G902" t="inlineStr">
@@ -43440,7 +43440,7 @@
       </c>
       <c r="F916" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="G916" t="inlineStr">
@@ -43490,7 +43490,7 @@
       </c>
       <c r="F917" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="G917" t="inlineStr">
@@ -43836,7 +43836,7 @@
       </c>
       <c r="F924" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="G924" t="inlineStr">
@@ -44128,7 +44128,7 @@
       </c>
       <c r="F930" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="G930" t="inlineStr">
@@ -45077,14 +45077,10 @@
       </c>
       <c r="G952" t="inlineStr">
         <is>
-          <t>16:40</t>
-        </is>
-      </c>
-      <c r="H952" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H952" t="inlineStr"/>
       <c r="I952" t="inlineStr"/>
       <c r="J952" t="inlineStr">
         <is>
@@ -46486,7 +46482,7 @@
       </c>
       <c r="F981" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="G981" t="inlineStr">
@@ -46586,7 +46582,7 @@
       </c>
       <c r="F983" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="G983" t="inlineStr">
@@ -47404,7 +47400,7 @@
       </c>
       <c r="F1000" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="G1000" t="inlineStr">
@@ -48344,7 +48340,7 @@
       </c>
       <c r="F1022" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="G1022" t="inlineStr">
@@ -48449,10 +48445,14 @@
       </c>
       <c r="G1024" t="inlineStr">
         <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H1024" t="inlineStr"/>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="H1024" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="I1024" t="inlineStr"/>
       <c r="J1024" t="inlineStr">
         <is>
@@ -48544,7 +48544,7 @@
       </c>
       <c r="F1026" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="G1026" t="inlineStr">
@@ -48686,7 +48686,7 @@
       </c>
       <c r="F1029" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="G1029" t="inlineStr">
@@ -48791,14 +48791,10 @@
       </c>
       <c r="G1031" t="inlineStr">
         <is>
-          <t>16:40</t>
-        </is>
-      </c>
-      <c r="H1031" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H1031" t="inlineStr"/>
       <c r="I1031" t="inlineStr"/>
       <c r="J1031" t="inlineStr">
         <is>
@@ -48974,7 +48970,7 @@
       </c>
       <c r="F1035" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="G1035" t="inlineStr">
@@ -49805,10 +49801,14 @@
       </c>
       <c r="G1052" t="inlineStr">
         <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H1052" t="inlineStr"/>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="H1052" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="I1052" t="inlineStr"/>
       <c r="J1052" t="inlineStr">
         <is>
@@ -50146,7 +50146,7 @@
       </c>
       <c r="F1059" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="G1059" t="inlineStr">
@@ -50580,7 +50580,7 @@
       </c>
       <c r="F1068" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="G1068" t="inlineStr">
@@ -50630,7 +50630,7 @@
       </c>
       <c r="F1069" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="G1069" t="inlineStr">
@@ -51820,7 +51820,7 @@
       </c>
       <c r="F1096" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="G1096" t="inlineStr">
@@ -52538,7 +52538,7 @@
       </c>
       <c r="F1111" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="G1111" t="inlineStr">
@@ -53134,7 +53134,7 @@
       </c>
       <c r="F1123" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="G1123" t="inlineStr">
@@ -54950,7 +54950,7 @@
       </c>
       <c r="F1163" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="G1163" t="inlineStr">
@@ -55684,7 +55684,7 @@
       </c>
       <c r="F1178" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="G1178" t="inlineStr">
@@ -56076,7 +56076,7 @@
       </c>
       <c r="F1186" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="G1186" t="inlineStr">
@@ -56218,7 +56218,7 @@
       </c>
       <c r="F1189" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="G1189" t="inlineStr">
@@ -56515,10 +56515,14 @@
       </c>
       <c r="G1195" t="inlineStr">
         <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="H1195" t="inlineStr"/>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="H1195" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="I1195" t="inlineStr"/>
       <c r="J1195" t="inlineStr">
         <is>
@@ -56944,7 +56948,7 @@
       </c>
       <c r="F1204" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="G1204" t="inlineStr">
@@ -57044,7 +57048,7 @@
       </c>
       <c r="F1206" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="G1206" t="inlineStr">
@@ -58610,7 +58614,7 @@
       </c>
       <c r="F1241" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="G1241" t="inlineStr">
@@ -59345,10 +59349,14 @@
       </c>
       <c r="G1256" t="inlineStr">
         <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H1256" t="inlineStr"/>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="H1256" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="I1256" t="inlineStr"/>
       <c r="J1256" t="inlineStr">
         <is>
@@ -59874,7 +59882,7 @@
       </c>
       <c r="F1267" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="G1267" t="inlineStr">
@@ -60287,10 +60295,14 @@
       </c>
       <c r="G1275" t="inlineStr">
         <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="H1275" t="inlineStr"/>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="H1275" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="I1275" t="inlineStr"/>
       <c r="J1275" t="inlineStr">
         <is>
@@ -61614,7 +61626,7 @@
       </c>
       <c r="F1305" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="G1305" t="inlineStr">
@@ -62506,7 +62518,7 @@
       </c>
       <c r="F1323" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="G1323" t="inlineStr">
@@ -62561,14 +62573,10 @@
       </c>
       <c r="G1324" t="inlineStr">
         <is>
-          <t>16:40</t>
-        </is>
-      </c>
-      <c r="H1324" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H1324" t="inlineStr"/>
       <c r="I1324" t="inlineStr"/>
       <c r="J1324" t="inlineStr">
         <is>
@@ -62610,7 +62618,7 @@
       </c>
       <c r="F1325" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="G1325" t="inlineStr">
@@ -62852,7 +62860,7 @@
       </c>
       <c r="F1330" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="G1330" t="inlineStr">
@@ -62902,7 +62910,7 @@
       </c>
       <c r="F1331" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="G1331" t="inlineStr">
@@ -63737,14 +63745,10 @@
       </c>
       <c r="G1348" t="inlineStr">
         <is>
-          <t>16:40</t>
-        </is>
-      </c>
-      <c r="H1348" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H1348" t="inlineStr"/>
       <c r="I1348" t="inlineStr"/>
       <c r="J1348" t="inlineStr">
         <is>
@@ -63836,7 +63840,7 @@
       </c>
       <c r="F1350" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="G1350" t="inlineStr">
@@ -64981,10 +64985,14 @@
       </c>
       <c r="G1376" t="inlineStr">
         <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="H1376" t="inlineStr"/>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="H1376" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="I1376" t="inlineStr"/>
       <c r="J1376" t="inlineStr">
         <is>
@@ -65240,6 +65248,6082 @@
         </is>
       </c>
     </row>
+    <row r="1382">
+      <c r="A1382" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B1382" t="inlineStr">
+        <is>
+          <t>Franklin</t>
+        </is>
+      </c>
+      <c r="C1382" t="inlineStr">
+        <is>
+          <t>Moris</t>
+        </is>
+      </c>
+      <c r="D1382" t="inlineStr">
+        <is>
+          <t>1-00001</t>
+        </is>
+      </c>
+      <c r="E1382" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="F1382" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="G1382" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H1382" t="inlineStr"/>
+      <c r="I1382" t="inlineStr"/>
+      <c r="J1382" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1382" t="inlineStr"/>
+      <c r="L1382" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1383">
+      <c r="A1383" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B1383" t="inlineStr">
+        <is>
+          <t>Gwen Atasha</t>
+        </is>
+      </c>
+      <c r="C1383" t="inlineStr">
+        <is>
+          <t>Lumagbas</t>
+        </is>
+      </c>
+      <c r="D1383" t="inlineStr">
+        <is>
+          <t>1-00002</t>
+        </is>
+      </c>
+      <c r="E1383" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="F1383" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="G1383" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H1383" t="inlineStr"/>
+      <c r="I1383" t="inlineStr"/>
+      <c r="J1383" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1383" t="inlineStr"/>
+      <c r="L1383" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1384">
+      <c r="A1384" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B1384" t="inlineStr">
+        <is>
+          <t>Maron</t>
+        </is>
+      </c>
+      <c r="C1384" t="inlineStr">
+        <is>
+          <t>Javier</t>
+        </is>
+      </c>
+      <c r="D1384" t="inlineStr">
+        <is>
+          <t>1-00003</t>
+        </is>
+      </c>
+      <c r="E1384" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="F1384" t="inlineStr"/>
+      <c r="G1384" t="inlineStr"/>
+      <c r="H1384" t="inlineStr"/>
+      <c r="I1384" t="inlineStr"/>
+      <c r="J1384" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1384" t="inlineStr"/>
+      <c r="L1384" t="inlineStr">
+        <is>
+          <t>Restday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1385">
+      <c r="A1385" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B1385" t="inlineStr">
+        <is>
+          <t>Elena</t>
+        </is>
+      </c>
+      <c r="C1385" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="D1385" t="inlineStr">
+        <is>
+          <t>1-00004</t>
+        </is>
+      </c>
+      <c r="E1385" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="F1385" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="G1385" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="H1385" t="inlineStr"/>
+      <c r="I1385" t="inlineStr"/>
+      <c r="J1385" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1385" t="inlineStr"/>
+      <c r="L1385" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1386">
+      <c r="A1386" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B1386" t="inlineStr">
+        <is>
+          <t>Miguel</t>
+        </is>
+      </c>
+      <c r="C1386" t="inlineStr">
+        <is>
+          <t>Reyes</t>
+        </is>
+      </c>
+      <c r="D1386" t="inlineStr">
+        <is>
+          <t>1-00005</t>
+        </is>
+      </c>
+      <c r="E1386" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="F1386" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="G1386" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H1386" t="inlineStr"/>
+      <c r="I1386" t="inlineStr"/>
+      <c r="J1386" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1386" t="inlineStr"/>
+      <c r="L1386" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1387">
+      <c r="A1387" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B1387" t="inlineStr">
+        <is>
+          <t>Ana</t>
+        </is>
+      </c>
+      <c r="C1387" t="inlineStr">
+        <is>
+          <t>Cruz</t>
+        </is>
+      </c>
+      <c r="D1387" t="inlineStr">
+        <is>
+          <t>1-00006</t>
+        </is>
+      </c>
+      <c r="E1387" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="F1387" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="G1387" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H1387" t="inlineStr"/>
+      <c r="I1387" t="inlineStr"/>
+      <c r="J1387" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1387" t="inlineStr"/>
+      <c r="L1387" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1388">
+      <c r="A1388" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B1388" t="inlineStr">
+        <is>
+          <t>Roberto</t>
+        </is>
+      </c>
+      <c r="C1388" t="inlineStr">
+        <is>
+          <t>Lim</t>
+        </is>
+      </c>
+      <c r="D1388" t="inlineStr">
+        <is>
+          <t>1-00007</t>
+        </is>
+      </c>
+      <c r="E1388" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="F1388" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="G1388" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H1388" t="inlineStr"/>
+      <c r="I1388" t="inlineStr"/>
+      <c r="J1388" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1388" t="inlineStr"/>
+      <c r="L1388" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1389">
+      <c r="A1389" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B1389" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="C1389" t="inlineStr">
+        <is>
+          <t>Gonzales</t>
+        </is>
+      </c>
+      <c r="D1389" t="inlineStr">
+        <is>
+          <t>1-00008</t>
+        </is>
+      </c>
+      <c r="E1389" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="F1389" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G1389" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="H1389" t="inlineStr"/>
+      <c r="I1389" t="inlineStr"/>
+      <c r="J1389" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1389" t="inlineStr"/>
+      <c r="L1389" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1390">
+      <c r="A1390" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B1390" t="inlineStr">
+        <is>
+          <t>James</t>
+        </is>
+      </c>
+      <c r="C1390" t="inlineStr">
+        <is>
+          <t>Villanueva</t>
+        </is>
+      </c>
+      <c r="D1390" t="inlineStr">
+        <is>
+          <t>1-00009</t>
+        </is>
+      </c>
+      <c r="E1390" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="F1390" t="inlineStr"/>
+      <c r="G1390" t="inlineStr"/>
+      <c r="H1390" t="inlineStr"/>
+      <c r="I1390" t="inlineStr"/>
+      <c r="J1390" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1390" t="inlineStr"/>
+      <c r="L1390" t="inlineStr">
+        <is>
+          <t>Restday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1391">
+      <c r="A1391" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B1391" t="inlineStr">
+        <is>
+          <t>Patricia</t>
+        </is>
+      </c>
+      <c r="C1391" t="inlineStr">
+        <is>
+          <t>Ng</t>
+        </is>
+      </c>
+      <c r="D1391" t="inlineStr">
+        <is>
+          <t>1-00010</t>
+        </is>
+      </c>
+      <c r="E1391" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="F1391" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="G1391" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H1391" t="inlineStr"/>
+      <c r="I1391" t="inlineStr"/>
+      <c r="J1391" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1391" t="inlineStr"/>
+      <c r="L1391" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1392">
+      <c r="A1392" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B1392" t="inlineStr">
+        <is>
+          <t>Franklin</t>
+        </is>
+      </c>
+      <c r="C1392" t="inlineStr">
+        <is>
+          <t>Moris</t>
+        </is>
+      </c>
+      <c r="D1392" t="inlineStr">
+        <is>
+          <t>1-00001</t>
+        </is>
+      </c>
+      <c r="E1392" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="F1392" t="inlineStr">
+        <is>
+          <t>08:17</t>
+        </is>
+      </c>
+      <c r="G1392" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H1392" t="inlineStr"/>
+      <c r="I1392" t="inlineStr"/>
+      <c r="J1392" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1392" t="inlineStr"/>
+      <c r="L1392" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1393">
+      <c r="A1393" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B1393" t="inlineStr">
+        <is>
+          <t>Gwen Atasha</t>
+        </is>
+      </c>
+      <c r="C1393" t="inlineStr">
+        <is>
+          <t>Lumagbas</t>
+        </is>
+      </c>
+      <c r="D1393" t="inlineStr">
+        <is>
+          <t>1-00002</t>
+        </is>
+      </c>
+      <c r="E1393" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="F1393" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="G1393" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H1393" t="inlineStr"/>
+      <c r="I1393" t="inlineStr"/>
+      <c r="J1393" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1393" t="inlineStr"/>
+      <c r="L1393" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1394">
+      <c r="A1394" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B1394" t="inlineStr">
+        <is>
+          <t>Maron</t>
+        </is>
+      </c>
+      <c r="C1394" t="inlineStr">
+        <is>
+          <t>Javier</t>
+        </is>
+      </c>
+      <c r="D1394" t="inlineStr">
+        <is>
+          <t>1-00003</t>
+        </is>
+      </c>
+      <c r="E1394" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="F1394" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="G1394" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H1394" t="inlineStr"/>
+      <c r="I1394" t="inlineStr"/>
+      <c r="J1394" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1394" t="inlineStr"/>
+      <c r="L1394" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1395">
+      <c r="A1395" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B1395" t="inlineStr">
+        <is>
+          <t>Elena</t>
+        </is>
+      </c>
+      <c r="C1395" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="D1395" t="inlineStr">
+        <is>
+          <t>1-00004</t>
+        </is>
+      </c>
+      <c r="E1395" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="F1395" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="G1395" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="H1395" t="inlineStr"/>
+      <c r="I1395" t="inlineStr"/>
+      <c r="J1395" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1395" t="inlineStr"/>
+      <c r="L1395" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1396">
+      <c r="A1396" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B1396" t="inlineStr">
+        <is>
+          <t>Miguel</t>
+        </is>
+      </c>
+      <c r="C1396" t="inlineStr">
+        <is>
+          <t>Reyes</t>
+        </is>
+      </c>
+      <c r="D1396" t="inlineStr">
+        <is>
+          <t>1-00005</t>
+        </is>
+      </c>
+      <c r="E1396" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="F1396" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="G1396" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H1396" t="inlineStr"/>
+      <c r="I1396" t="inlineStr"/>
+      <c r="J1396" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1396" t="inlineStr"/>
+      <c r="L1396" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1397">
+      <c r="A1397" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B1397" t="inlineStr">
+        <is>
+          <t>Ana</t>
+        </is>
+      </c>
+      <c r="C1397" t="inlineStr">
+        <is>
+          <t>Cruz</t>
+        </is>
+      </c>
+      <c r="D1397" t="inlineStr">
+        <is>
+          <t>1-00006</t>
+        </is>
+      </c>
+      <c r="E1397" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="F1397" t="inlineStr"/>
+      <c r="G1397" t="inlineStr"/>
+      <c r="H1397" t="inlineStr"/>
+      <c r="I1397" t="inlineStr"/>
+      <c r="J1397" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1397" t="inlineStr"/>
+      <c r="L1397" t="inlineStr">
+        <is>
+          <t>Restday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1398">
+      <c r="A1398" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B1398" t="inlineStr">
+        <is>
+          <t>Roberto</t>
+        </is>
+      </c>
+      <c r="C1398" t="inlineStr">
+        <is>
+          <t>Lim</t>
+        </is>
+      </c>
+      <c r="D1398" t="inlineStr">
+        <is>
+          <t>1-00007</t>
+        </is>
+      </c>
+      <c r="E1398" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="F1398" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="G1398" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H1398" t="inlineStr"/>
+      <c r="I1398" t="inlineStr"/>
+      <c r="J1398" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1398" t="inlineStr"/>
+      <c r="L1398" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1399">
+      <c r="A1399" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B1399" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="C1399" t="inlineStr">
+        <is>
+          <t>Gonzales</t>
+        </is>
+      </c>
+      <c r="D1399" t="inlineStr">
+        <is>
+          <t>1-00008</t>
+        </is>
+      </c>
+      <c r="E1399" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="F1399" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G1399" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="H1399" t="inlineStr"/>
+      <c r="I1399" t="inlineStr"/>
+      <c r="J1399" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1399" t="inlineStr"/>
+      <c r="L1399" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1400">
+      <c r="A1400" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B1400" t="inlineStr">
+        <is>
+          <t>James</t>
+        </is>
+      </c>
+      <c r="C1400" t="inlineStr">
+        <is>
+          <t>Villanueva</t>
+        </is>
+      </c>
+      <c r="D1400" t="inlineStr">
+        <is>
+          <t>1-00009</t>
+        </is>
+      </c>
+      <c r="E1400" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="F1400" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="G1400" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H1400" t="inlineStr"/>
+      <c r="I1400" t="inlineStr"/>
+      <c r="J1400" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1400" t="inlineStr"/>
+      <c r="L1400" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1401">
+      <c r="A1401" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B1401" t="inlineStr">
+        <is>
+          <t>Patricia</t>
+        </is>
+      </c>
+      <c r="C1401" t="inlineStr">
+        <is>
+          <t>Ng</t>
+        </is>
+      </c>
+      <c r="D1401" t="inlineStr">
+        <is>
+          <t>1-00010</t>
+        </is>
+      </c>
+      <c r="E1401" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="F1401" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="G1401" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H1401" t="inlineStr"/>
+      <c r="I1401" t="inlineStr"/>
+      <c r="J1401" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1401" t="inlineStr"/>
+      <c r="L1401" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1402">
+      <c r="A1402" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B1402" t="inlineStr">
+        <is>
+          <t>Franklin</t>
+        </is>
+      </c>
+      <c r="C1402" t="inlineStr">
+        <is>
+          <t>Moris</t>
+        </is>
+      </c>
+      <c r="D1402" t="inlineStr">
+        <is>
+          <t>1-00001</t>
+        </is>
+      </c>
+      <c r="E1402" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="F1402" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="G1402" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H1402" t="inlineStr"/>
+      <c r="I1402" t="inlineStr"/>
+      <c r="J1402" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1402" t="inlineStr"/>
+      <c r="L1402" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1403">
+      <c r="A1403" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B1403" t="inlineStr">
+        <is>
+          <t>Gwen Atasha</t>
+        </is>
+      </c>
+      <c r="C1403" t="inlineStr">
+        <is>
+          <t>Lumagbas</t>
+        </is>
+      </c>
+      <c r="D1403" t="inlineStr">
+        <is>
+          <t>1-00002</t>
+        </is>
+      </c>
+      <c r="E1403" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="F1403" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="G1403" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H1403" t="inlineStr"/>
+      <c r="I1403" t="inlineStr"/>
+      <c r="J1403" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1403" t="inlineStr"/>
+      <c r="L1403" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1404">
+      <c r="A1404" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B1404" t="inlineStr">
+        <is>
+          <t>Maron</t>
+        </is>
+      </c>
+      <c r="C1404" t="inlineStr">
+        <is>
+          <t>Javier</t>
+        </is>
+      </c>
+      <c r="D1404" t="inlineStr">
+        <is>
+          <t>1-00003</t>
+        </is>
+      </c>
+      <c r="E1404" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="F1404" t="inlineStr"/>
+      <c r="G1404" t="inlineStr"/>
+      <c r="H1404" t="inlineStr"/>
+      <c r="I1404" t="inlineStr"/>
+      <c r="J1404" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1404" t="inlineStr"/>
+      <c r="L1404" t="inlineStr">
+        <is>
+          <t>Restday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1405">
+      <c r="A1405" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B1405" t="inlineStr">
+        <is>
+          <t>Elena</t>
+        </is>
+      </c>
+      <c r="C1405" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="D1405" t="inlineStr">
+        <is>
+          <t>1-00004</t>
+        </is>
+      </c>
+      <c r="E1405" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="F1405" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="G1405" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="H1405" t="inlineStr"/>
+      <c r="I1405" t="inlineStr"/>
+      <c r="J1405" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1405" t="inlineStr"/>
+      <c r="L1405" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1406">
+      <c r="A1406" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B1406" t="inlineStr">
+        <is>
+          <t>Miguel</t>
+        </is>
+      </c>
+      <c r="C1406" t="inlineStr">
+        <is>
+          <t>Reyes</t>
+        </is>
+      </c>
+      <c r="D1406" t="inlineStr">
+        <is>
+          <t>1-00005</t>
+        </is>
+      </c>
+      <c r="E1406" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="F1406" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="G1406" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H1406" t="inlineStr"/>
+      <c r="I1406" t="inlineStr"/>
+      <c r="J1406" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1406" t="inlineStr"/>
+      <c r="L1406" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1407">
+      <c r="A1407" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B1407" t="inlineStr">
+        <is>
+          <t>Ana</t>
+        </is>
+      </c>
+      <c r="C1407" t="inlineStr">
+        <is>
+          <t>Cruz</t>
+        </is>
+      </c>
+      <c r="D1407" t="inlineStr">
+        <is>
+          <t>1-00006</t>
+        </is>
+      </c>
+      <c r="E1407" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="F1407" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="G1407" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H1407" t="inlineStr"/>
+      <c r="I1407" t="inlineStr"/>
+      <c r="J1407" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1407" t="inlineStr"/>
+      <c r="L1407" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1408">
+      <c r="A1408" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B1408" t="inlineStr">
+        <is>
+          <t>Roberto</t>
+        </is>
+      </c>
+      <c r="C1408" t="inlineStr">
+        <is>
+          <t>Lim</t>
+        </is>
+      </c>
+      <c r="D1408" t="inlineStr">
+        <is>
+          <t>1-00007</t>
+        </is>
+      </c>
+      <c r="E1408" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="F1408" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="G1408" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H1408" t="inlineStr"/>
+      <c r="I1408" t="inlineStr"/>
+      <c r="J1408" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1408" t="inlineStr"/>
+      <c r="L1408" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1409">
+      <c r="A1409" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B1409" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="C1409" t="inlineStr">
+        <is>
+          <t>Gonzales</t>
+        </is>
+      </c>
+      <c r="D1409" t="inlineStr">
+        <is>
+          <t>1-00008</t>
+        </is>
+      </c>
+      <c r="E1409" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="F1409" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="G1409" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="H1409" t="inlineStr"/>
+      <c r="I1409" t="inlineStr"/>
+      <c r="J1409" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1409" t="inlineStr"/>
+      <c r="L1409" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1410">
+      <c r="A1410" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B1410" t="inlineStr">
+        <is>
+          <t>James</t>
+        </is>
+      </c>
+      <c r="C1410" t="inlineStr">
+        <is>
+          <t>Villanueva</t>
+        </is>
+      </c>
+      <c r="D1410" t="inlineStr">
+        <is>
+          <t>1-00009</t>
+        </is>
+      </c>
+      <c r="E1410" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="F1410" t="inlineStr"/>
+      <c r="G1410" t="inlineStr"/>
+      <c r="H1410" t="inlineStr"/>
+      <c r="I1410" t="inlineStr"/>
+      <c r="J1410" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1410" t="inlineStr"/>
+      <c r="L1410" t="inlineStr">
+        <is>
+          <t>Restday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1411">
+      <c r="A1411" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B1411" t="inlineStr">
+        <is>
+          <t>Patricia</t>
+        </is>
+      </c>
+      <c r="C1411" t="inlineStr">
+        <is>
+          <t>Ng</t>
+        </is>
+      </c>
+      <c r="D1411" t="inlineStr">
+        <is>
+          <t>1-00010</t>
+        </is>
+      </c>
+      <c r="E1411" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="F1411" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="G1411" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H1411" t="inlineStr"/>
+      <c r="I1411" t="inlineStr"/>
+      <c r="J1411" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1411" t="inlineStr"/>
+      <c r="L1411" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1412">
+      <c r="A1412" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B1412" t="inlineStr">
+        <is>
+          <t>Franklin</t>
+        </is>
+      </c>
+      <c r="C1412" t="inlineStr">
+        <is>
+          <t>Moris</t>
+        </is>
+      </c>
+      <c r="D1412" t="inlineStr">
+        <is>
+          <t>1-00001</t>
+        </is>
+      </c>
+      <c r="E1412" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="F1412" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="G1412" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H1412" t="inlineStr"/>
+      <c r="I1412" t="inlineStr"/>
+      <c r="J1412" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1412" t="inlineStr"/>
+      <c r="L1412" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1413">
+      <c r="A1413" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B1413" t="inlineStr">
+        <is>
+          <t>Gwen Atasha</t>
+        </is>
+      </c>
+      <c r="C1413" t="inlineStr">
+        <is>
+          <t>Lumagbas</t>
+        </is>
+      </c>
+      <c r="D1413" t="inlineStr">
+        <is>
+          <t>1-00002</t>
+        </is>
+      </c>
+      <c r="E1413" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="F1413" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="G1413" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H1413" t="inlineStr"/>
+      <c r="I1413" t="inlineStr"/>
+      <c r="J1413" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1413" t="inlineStr"/>
+      <c r="L1413" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1414">
+      <c r="A1414" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B1414" t="inlineStr">
+        <is>
+          <t>Maron</t>
+        </is>
+      </c>
+      <c r="C1414" t="inlineStr">
+        <is>
+          <t>Javier</t>
+        </is>
+      </c>
+      <c r="D1414" t="inlineStr">
+        <is>
+          <t>1-00003</t>
+        </is>
+      </c>
+      <c r="E1414" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="F1414" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="G1414" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H1414" t="inlineStr"/>
+      <c r="I1414" t="inlineStr"/>
+      <c r="J1414" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1414" t="inlineStr"/>
+      <c r="L1414" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1415">
+      <c r="A1415" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B1415" t="inlineStr">
+        <is>
+          <t>Elena</t>
+        </is>
+      </c>
+      <c r="C1415" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="D1415" t="inlineStr">
+        <is>
+          <t>1-00004</t>
+        </is>
+      </c>
+      <c r="E1415" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="F1415" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="G1415" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="H1415" t="inlineStr"/>
+      <c r="I1415" t="inlineStr"/>
+      <c r="J1415" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1415" t="inlineStr"/>
+      <c r="L1415" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1416">
+      <c r="A1416" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B1416" t="inlineStr">
+        <is>
+          <t>Miguel</t>
+        </is>
+      </c>
+      <c r="C1416" t="inlineStr">
+        <is>
+          <t>Reyes</t>
+        </is>
+      </c>
+      <c r="D1416" t="inlineStr">
+        <is>
+          <t>1-00005</t>
+        </is>
+      </c>
+      <c r="E1416" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="F1416" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="G1416" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H1416" t="inlineStr"/>
+      <c r="I1416" t="inlineStr"/>
+      <c r="J1416" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1416" t="inlineStr"/>
+      <c r="L1416" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1417">
+      <c r="A1417" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B1417" t="inlineStr">
+        <is>
+          <t>Ana</t>
+        </is>
+      </c>
+      <c r="C1417" t="inlineStr">
+        <is>
+          <t>Cruz</t>
+        </is>
+      </c>
+      <c r="D1417" t="inlineStr">
+        <is>
+          <t>1-00006</t>
+        </is>
+      </c>
+      <c r="E1417" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="F1417" t="inlineStr"/>
+      <c r="G1417" t="inlineStr"/>
+      <c r="H1417" t="inlineStr"/>
+      <c r="I1417" t="inlineStr"/>
+      <c r="J1417" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1417" t="inlineStr"/>
+      <c r="L1417" t="inlineStr">
+        <is>
+          <t>Restday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1418">
+      <c r="A1418" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B1418" t="inlineStr">
+        <is>
+          <t>Roberto</t>
+        </is>
+      </c>
+      <c r="C1418" t="inlineStr">
+        <is>
+          <t>Lim</t>
+        </is>
+      </c>
+      <c r="D1418" t="inlineStr">
+        <is>
+          <t>1-00007</t>
+        </is>
+      </c>
+      <c r="E1418" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="F1418" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="G1418" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H1418" t="inlineStr"/>
+      <c r="I1418" t="inlineStr"/>
+      <c r="J1418" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1418" t="inlineStr"/>
+      <c r="L1418" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1419">
+      <c r="A1419" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B1419" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="C1419" t="inlineStr">
+        <is>
+          <t>Gonzales</t>
+        </is>
+      </c>
+      <c r="D1419" t="inlineStr">
+        <is>
+          <t>1-00008</t>
+        </is>
+      </c>
+      <c r="E1419" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="F1419" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G1419" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="H1419" t="inlineStr"/>
+      <c r="I1419" t="inlineStr"/>
+      <c r="J1419" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1419" t="inlineStr"/>
+      <c r="L1419" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1420">
+      <c r="A1420" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B1420" t="inlineStr">
+        <is>
+          <t>James</t>
+        </is>
+      </c>
+      <c r="C1420" t="inlineStr">
+        <is>
+          <t>Villanueva</t>
+        </is>
+      </c>
+      <c r="D1420" t="inlineStr">
+        <is>
+          <t>1-00009</t>
+        </is>
+      </c>
+      <c r="E1420" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="F1420" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="G1420" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H1420" t="inlineStr"/>
+      <c r="I1420" t="inlineStr"/>
+      <c r="J1420" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1420" t="inlineStr"/>
+      <c r="L1420" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1421">
+      <c r="A1421" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B1421" t="inlineStr">
+        <is>
+          <t>Patricia</t>
+        </is>
+      </c>
+      <c r="C1421" t="inlineStr">
+        <is>
+          <t>Ng</t>
+        </is>
+      </c>
+      <c r="D1421" t="inlineStr">
+        <is>
+          <t>1-00010</t>
+        </is>
+      </c>
+      <c r="E1421" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="F1421" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="G1421" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H1421" t="inlineStr"/>
+      <c r="I1421" t="inlineStr"/>
+      <c r="J1421" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1421" t="inlineStr"/>
+      <c r="L1421" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1422">
+      <c r="A1422" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B1422" t="inlineStr">
+        <is>
+          <t>Franklin</t>
+        </is>
+      </c>
+      <c r="C1422" t="inlineStr">
+        <is>
+          <t>Moris</t>
+        </is>
+      </c>
+      <c r="D1422" t="inlineStr">
+        <is>
+          <t>1-00001</t>
+        </is>
+      </c>
+      <c r="E1422" t="inlineStr">
+        <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="F1422" t="inlineStr"/>
+      <c r="G1422" t="inlineStr"/>
+      <c r="H1422" t="inlineStr"/>
+      <c r="I1422" t="inlineStr"/>
+      <c r="J1422" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1422" t="inlineStr"/>
+      <c r="L1422" t="inlineStr">
+        <is>
+          <t>Restday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1423">
+      <c r="A1423" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B1423" t="inlineStr">
+        <is>
+          <t>Gwen Atasha</t>
+        </is>
+      </c>
+      <c r="C1423" t="inlineStr">
+        <is>
+          <t>Lumagbas</t>
+        </is>
+      </c>
+      <c r="D1423" t="inlineStr">
+        <is>
+          <t>1-00002</t>
+        </is>
+      </c>
+      <c r="E1423" t="inlineStr">
+        <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="F1423" t="inlineStr"/>
+      <c r="G1423" t="inlineStr"/>
+      <c r="H1423" t="inlineStr"/>
+      <c r="I1423" t="inlineStr"/>
+      <c r="J1423" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1423" t="inlineStr"/>
+      <c r="L1423" t="inlineStr">
+        <is>
+          <t>Restday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1424">
+      <c r="A1424" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B1424" t="inlineStr">
+        <is>
+          <t>Maron</t>
+        </is>
+      </c>
+      <c r="C1424" t="inlineStr">
+        <is>
+          <t>Javier</t>
+        </is>
+      </c>
+      <c r="D1424" t="inlineStr">
+        <is>
+          <t>1-00003</t>
+        </is>
+      </c>
+      <c r="E1424" t="inlineStr">
+        <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="F1424" t="inlineStr"/>
+      <c r="G1424" t="inlineStr"/>
+      <c r="H1424" t="inlineStr"/>
+      <c r="I1424" t="inlineStr"/>
+      <c r="J1424" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1424" t="inlineStr"/>
+      <c r="L1424" t="inlineStr">
+        <is>
+          <t>Restday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1425">
+      <c r="A1425" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B1425" t="inlineStr">
+        <is>
+          <t>Elena</t>
+        </is>
+      </c>
+      <c r="C1425" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="D1425" t="inlineStr">
+        <is>
+          <t>1-00004</t>
+        </is>
+      </c>
+      <c r="E1425" t="inlineStr">
+        <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="F1425" t="inlineStr"/>
+      <c r="G1425" t="inlineStr"/>
+      <c r="H1425" t="inlineStr"/>
+      <c r="I1425" t="inlineStr"/>
+      <c r="J1425" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1425" t="inlineStr"/>
+      <c r="L1425" t="inlineStr">
+        <is>
+          <t>Restday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1426">
+      <c r="A1426" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B1426" t="inlineStr">
+        <is>
+          <t>Miguel</t>
+        </is>
+      </c>
+      <c r="C1426" t="inlineStr">
+        <is>
+          <t>Reyes</t>
+        </is>
+      </c>
+      <c r="D1426" t="inlineStr">
+        <is>
+          <t>1-00005</t>
+        </is>
+      </c>
+      <c r="E1426" t="inlineStr">
+        <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="F1426" t="inlineStr"/>
+      <c r="G1426" t="inlineStr"/>
+      <c r="H1426" t="inlineStr"/>
+      <c r="I1426" t="inlineStr"/>
+      <c r="J1426" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1426" t="inlineStr"/>
+      <c r="L1426" t="inlineStr">
+        <is>
+          <t>Restday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1427">
+      <c r="A1427" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B1427" t="inlineStr">
+        <is>
+          <t>Ana</t>
+        </is>
+      </c>
+      <c r="C1427" t="inlineStr">
+        <is>
+          <t>Cruz</t>
+        </is>
+      </c>
+      <c r="D1427" t="inlineStr">
+        <is>
+          <t>1-00006</t>
+        </is>
+      </c>
+      <c r="E1427" t="inlineStr">
+        <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="F1427" t="inlineStr"/>
+      <c r="G1427" t="inlineStr"/>
+      <c r="H1427" t="inlineStr"/>
+      <c r="I1427" t="inlineStr"/>
+      <c r="J1427" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1427" t="inlineStr"/>
+      <c r="L1427" t="inlineStr">
+        <is>
+          <t>Restday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1428">
+      <c r="A1428" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B1428" t="inlineStr">
+        <is>
+          <t>Roberto</t>
+        </is>
+      </c>
+      <c r="C1428" t="inlineStr">
+        <is>
+          <t>Lim</t>
+        </is>
+      </c>
+      <c r="D1428" t="inlineStr">
+        <is>
+          <t>1-00007</t>
+        </is>
+      </c>
+      <c r="E1428" t="inlineStr">
+        <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="F1428" t="inlineStr"/>
+      <c r="G1428" t="inlineStr"/>
+      <c r="H1428" t="inlineStr"/>
+      <c r="I1428" t="inlineStr"/>
+      <c r="J1428" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1428" t="inlineStr"/>
+      <c r="L1428" t="inlineStr">
+        <is>
+          <t>Restday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1429">
+      <c r="A1429" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B1429" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="C1429" t="inlineStr">
+        <is>
+          <t>Gonzales</t>
+        </is>
+      </c>
+      <c r="D1429" t="inlineStr">
+        <is>
+          <t>1-00008</t>
+        </is>
+      </c>
+      <c r="E1429" t="inlineStr">
+        <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="F1429" t="inlineStr"/>
+      <c r="G1429" t="inlineStr"/>
+      <c r="H1429" t="inlineStr"/>
+      <c r="I1429" t="inlineStr"/>
+      <c r="J1429" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1429" t="inlineStr"/>
+      <c r="L1429" t="inlineStr">
+        <is>
+          <t>Restday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1430">
+      <c r="A1430" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B1430" t="inlineStr">
+        <is>
+          <t>James</t>
+        </is>
+      </c>
+      <c r="C1430" t="inlineStr">
+        <is>
+          <t>Villanueva</t>
+        </is>
+      </c>
+      <c r="D1430" t="inlineStr">
+        <is>
+          <t>1-00009</t>
+        </is>
+      </c>
+      <c r="E1430" t="inlineStr">
+        <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="F1430" t="inlineStr"/>
+      <c r="G1430" t="inlineStr"/>
+      <c r="H1430" t="inlineStr"/>
+      <c r="I1430" t="inlineStr"/>
+      <c r="J1430" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1430" t="inlineStr"/>
+      <c r="L1430" t="inlineStr">
+        <is>
+          <t>Restday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1431">
+      <c r="A1431" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B1431" t="inlineStr">
+        <is>
+          <t>Patricia</t>
+        </is>
+      </c>
+      <c r="C1431" t="inlineStr">
+        <is>
+          <t>Ng</t>
+        </is>
+      </c>
+      <c r="D1431" t="inlineStr">
+        <is>
+          <t>1-00010</t>
+        </is>
+      </c>
+      <c r="E1431" t="inlineStr">
+        <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="F1431" t="inlineStr"/>
+      <c r="G1431" t="inlineStr"/>
+      <c r="H1431" t="inlineStr"/>
+      <c r="I1431" t="inlineStr"/>
+      <c r="J1431" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1431" t="inlineStr"/>
+      <c r="L1431" t="inlineStr">
+        <is>
+          <t>Restday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1432">
+      <c r="A1432" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B1432" t="inlineStr">
+        <is>
+          <t>Franklin</t>
+        </is>
+      </c>
+      <c r="C1432" t="inlineStr">
+        <is>
+          <t>Moris</t>
+        </is>
+      </c>
+      <c r="D1432" t="inlineStr">
+        <is>
+          <t>1-00001</t>
+        </is>
+      </c>
+      <c r="E1432" t="inlineStr">
+        <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="F1432" t="inlineStr"/>
+      <c r="G1432" t="inlineStr"/>
+      <c r="H1432" t="inlineStr"/>
+      <c r="I1432" t="inlineStr"/>
+      <c r="J1432" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1432" t="inlineStr"/>
+      <c r="L1432" t="inlineStr">
+        <is>
+          <t>Restday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1433">
+      <c r="A1433" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B1433" t="inlineStr">
+        <is>
+          <t>Gwen Atasha</t>
+        </is>
+      </c>
+      <c r="C1433" t="inlineStr">
+        <is>
+          <t>Lumagbas</t>
+        </is>
+      </c>
+      <c r="D1433" t="inlineStr">
+        <is>
+          <t>1-00002</t>
+        </is>
+      </c>
+      <c r="E1433" t="inlineStr">
+        <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="F1433" t="inlineStr"/>
+      <c r="G1433" t="inlineStr"/>
+      <c r="H1433" t="inlineStr"/>
+      <c r="I1433" t="inlineStr"/>
+      <c r="J1433" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1433" t="inlineStr"/>
+      <c r="L1433" t="inlineStr">
+        <is>
+          <t>Restday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1434">
+      <c r="A1434" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B1434" t="inlineStr">
+        <is>
+          <t>Maron</t>
+        </is>
+      </c>
+      <c r="C1434" t="inlineStr">
+        <is>
+          <t>Javier</t>
+        </is>
+      </c>
+      <c r="D1434" t="inlineStr">
+        <is>
+          <t>1-00003</t>
+        </is>
+      </c>
+      <c r="E1434" t="inlineStr">
+        <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="F1434" t="inlineStr"/>
+      <c r="G1434" t="inlineStr"/>
+      <c r="H1434" t="inlineStr"/>
+      <c r="I1434" t="inlineStr"/>
+      <c r="J1434" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1434" t="inlineStr"/>
+      <c r="L1434" t="inlineStr">
+        <is>
+          <t>Restday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1435">
+      <c r="A1435" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B1435" t="inlineStr">
+        <is>
+          <t>Elena</t>
+        </is>
+      </c>
+      <c r="C1435" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="D1435" t="inlineStr">
+        <is>
+          <t>1-00004</t>
+        </is>
+      </c>
+      <c r="E1435" t="inlineStr">
+        <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="F1435" t="inlineStr"/>
+      <c r="G1435" t="inlineStr"/>
+      <c r="H1435" t="inlineStr"/>
+      <c r="I1435" t="inlineStr"/>
+      <c r="J1435" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1435" t="inlineStr"/>
+      <c r="L1435" t="inlineStr">
+        <is>
+          <t>Restday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1436">
+      <c r="A1436" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B1436" t="inlineStr">
+        <is>
+          <t>Miguel</t>
+        </is>
+      </c>
+      <c r="C1436" t="inlineStr">
+        <is>
+          <t>Reyes</t>
+        </is>
+      </c>
+      <c r="D1436" t="inlineStr">
+        <is>
+          <t>1-00005</t>
+        </is>
+      </c>
+      <c r="E1436" t="inlineStr">
+        <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="F1436" t="inlineStr"/>
+      <c r="G1436" t="inlineStr"/>
+      <c r="H1436" t="inlineStr"/>
+      <c r="I1436" t="inlineStr"/>
+      <c r="J1436" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1436" t="inlineStr"/>
+      <c r="L1436" t="inlineStr">
+        <is>
+          <t>Restday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1437">
+      <c r="A1437" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B1437" t="inlineStr">
+        <is>
+          <t>Ana</t>
+        </is>
+      </c>
+      <c r="C1437" t="inlineStr">
+        <is>
+          <t>Cruz</t>
+        </is>
+      </c>
+      <c r="D1437" t="inlineStr">
+        <is>
+          <t>1-00006</t>
+        </is>
+      </c>
+      <c r="E1437" t="inlineStr">
+        <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="F1437" t="inlineStr"/>
+      <c r="G1437" t="inlineStr"/>
+      <c r="H1437" t="inlineStr"/>
+      <c r="I1437" t="inlineStr"/>
+      <c r="J1437" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1437" t="inlineStr"/>
+      <c r="L1437" t="inlineStr">
+        <is>
+          <t>Restday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1438">
+      <c r="A1438" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B1438" t="inlineStr">
+        <is>
+          <t>Roberto</t>
+        </is>
+      </c>
+      <c r="C1438" t="inlineStr">
+        <is>
+          <t>Lim</t>
+        </is>
+      </c>
+      <c r="D1438" t="inlineStr">
+        <is>
+          <t>1-00007</t>
+        </is>
+      </c>
+      <c r="E1438" t="inlineStr">
+        <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="F1438" t="inlineStr"/>
+      <c r="G1438" t="inlineStr"/>
+      <c r="H1438" t="inlineStr"/>
+      <c r="I1438" t="inlineStr"/>
+      <c r="J1438" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1438" t="inlineStr"/>
+      <c r="L1438" t="inlineStr">
+        <is>
+          <t>Restday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1439">
+      <c r="A1439" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B1439" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="C1439" t="inlineStr">
+        <is>
+          <t>Gonzales</t>
+        </is>
+      </c>
+      <c r="D1439" t="inlineStr">
+        <is>
+          <t>1-00008</t>
+        </is>
+      </c>
+      <c r="E1439" t="inlineStr">
+        <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="F1439" t="inlineStr"/>
+      <c r="G1439" t="inlineStr"/>
+      <c r="H1439" t="inlineStr"/>
+      <c r="I1439" t="inlineStr"/>
+      <c r="J1439" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1439" t="inlineStr"/>
+      <c r="L1439" t="inlineStr">
+        <is>
+          <t>Restday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1440">
+      <c r="A1440" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B1440" t="inlineStr">
+        <is>
+          <t>James</t>
+        </is>
+      </c>
+      <c r="C1440" t="inlineStr">
+        <is>
+          <t>Villanueva</t>
+        </is>
+      </c>
+      <c r="D1440" t="inlineStr">
+        <is>
+          <t>1-00009</t>
+        </is>
+      </c>
+      <c r="E1440" t="inlineStr">
+        <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="F1440" t="inlineStr"/>
+      <c r="G1440" t="inlineStr"/>
+      <c r="H1440" t="inlineStr"/>
+      <c r="I1440" t="inlineStr"/>
+      <c r="J1440" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1440" t="inlineStr"/>
+      <c r="L1440" t="inlineStr">
+        <is>
+          <t>Restday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1441">
+      <c r="A1441" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B1441" t="inlineStr">
+        <is>
+          <t>Patricia</t>
+        </is>
+      </c>
+      <c r="C1441" t="inlineStr">
+        <is>
+          <t>Ng</t>
+        </is>
+      </c>
+      <c r="D1441" t="inlineStr">
+        <is>
+          <t>1-00010</t>
+        </is>
+      </c>
+      <c r="E1441" t="inlineStr">
+        <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="F1441" t="inlineStr"/>
+      <c r="G1441" t="inlineStr"/>
+      <c r="H1441" t="inlineStr"/>
+      <c r="I1441" t="inlineStr"/>
+      <c r="J1441" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1441" t="inlineStr"/>
+      <c r="L1441" t="inlineStr">
+        <is>
+          <t>Restday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1442">
+      <c r="A1442" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B1442" t="inlineStr">
+        <is>
+          <t>Franklin</t>
+        </is>
+      </c>
+      <c r="C1442" t="inlineStr">
+        <is>
+          <t>Moris</t>
+        </is>
+      </c>
+      <c r="D1442" t="inlineStr">
+        <is>
+          <t>1-00001</t>
+        </is>
+      </c>
+      <c r="E1442" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="F1442" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="G1442" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H1442" t="inlineStr"/>
+      <c r="I1442" t="inlineStr"/>
+      <c r="J1442" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1442" t="inlineStr"/>
+      <c r="L1442" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1443">
+      <c r="A1443" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B1443" t="inlineStr">
+        <is>
+          <t>Gwen Atasha</t>
+        </is>
+      </c>
+      <c r="C1443" t="inlineStr">
+        <is>
+          <t>Lumagbas</t>
+        </is>
+      </c>
+      <c r="D1443" t="inlineStr">
+        <is>
+          <t>1-00002</t>
+        </is>
+      </c>
+      <c r="E1443" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="F1443" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="G1443" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H1443" t="inlineStr"/>
+      <c r="I1443" t="inlineStr"/>
+      <c r="J1443" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1443" t="inlineStr"/>
+      <c r="L1443" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1444">
+      <c r="A1444" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B1444" t="inlineStr">
+        <is>
+          <t>Maron</t>
+        </is>
+      </c>
+      <c r="C1444" t="inlineStr">
+        <is>
+          <t>Javier</t>
+        </is>
+      </c>
+      <c r="D1444" t="inlineStr">
+        <is>
+          <t>1-00003</t>
+        </is>
+      </c>
+      <c r="E1444" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="F1444" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="G1444" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H1444" t="inlineStr"/>
+      <c r="I1444" t="inlineStr"/>
+      <c r="J1444" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1444" t="inlineStr"/>
+      <c r="L1444" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1445">
+      <c r="A1445" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B1445" t="inlineStr">
+        <is>
+          <t>Elena</t>
+        </is>
+      </c>
+      <c r="C1445" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="D1445" t="inlineStr">
+        <is>
+          <t>1-00004</t>
+        </is>
+      </c>
+      <c r="E1445" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="F1445" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="G1445" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="H1445" t="inlineStr"/>
+      <c r="I1445" t="inlineStr"/>
+      <c r="J1445" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1445" t="inlineStr"/>
+      <c r="L1445" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1446">
+      <c r="A1446" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B1446" t="inlineStr">
+        <is>
+          <t>Miguel</t>
+        </is>
+      </c>
+      <c r="C1446" t="inlineStr">
+        <is>
+          <t>Reyes</t>
+        </is>
+      </c>
+      <c r="D1446" t="inlineStr">
+        <is>
+          <t>1-00005</t>
+        </is>
+      </c>
+      <c r="E1446" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="F1446" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="G1446" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H1446" t="inlineStr"/>
+      <c r="I1446" t="inlineStr"/>
+      <c r="J1446" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1446" t="inlineStr"/>
+      <c r="L1446" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1447">
+      <c r="A1447" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B1447" t="inlineStr">
+        <is>
+          <t>Ana</t>
+        </is>
+      </c>
+      <c r="C1447" t="inlineStr">
+        <is>
+          <t>Cruz</t>
+        </is>
+      </c>
+      <c r="D1447" t="inlineStr">
+        <is>
+          <t>1-00006</t>
+        </is>
+      </c>
+      <c r="E1447" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="F1447" t="inlineStr"/>
+      <c r="G1447" t="inlineStr"/>
+      <c r="H1447" t="inlineStr"/>
+      <c r="I1447" t="inlineStr"/>
+      <c r="J1447" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1447" t="inlineStr"/>
+      <c r="L1447" t="inlineStr">
+        <is>
+          <t>Restday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1448">
+      <c r="A1448" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B1448" t="inlineStr">
+        <is>
+          <t>Roberto</t>
+        </is>
+      </c>
+      <c r="C1448" t="inlineStr">
+        <is>
+          <t>Lim</t>
+        </is>
+      </c>
+      <c r="D1448" t="inlineStr">
+        <is>
+          <t>1-00007</t>
+        </is>
+      </c>
+      <c r="E1448" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="F1448" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="G1448" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H1448" t="inlineStr"/>
+      <c r="I1448" t="inlineStr"/>
+      <c r="J1448" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1448" t="inlineStr"/>
+      <c r="L1448" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1449">
+      <c r="A1449" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B1449" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="C1449" t="inlineStr">
+        <is>
+          <t>Gonzales</t>
+        </is>
+      </c>
+      <c r="D1449" t="inlineStr">
+        <is>
+          <t>1-00008</t>
+        </is>
+      </c>
+      <c r="E1449" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="F1449" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G1449" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="H1449" t="inlineStr"/>
+      <c r="I1449" t="inlineStr"/>
+      <c r="J1449" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1449" t="inlineStr"/>
+      <c r="L1449" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1450">
+      <c r="A1450" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B1450" t="inlineStr">
+        <is>
+          <t>James</t>
+        </is>
+      </c>
+      <c r="C1450" t="inlineStr">
+        <is>
+          <t>Villanueva</t>
+        </is>
+      </c>
+      <c r="D1450" t="inlineStr">
+        <is>
+          <t>1-00009</t>
+        </is>
+      </c>
+      <c r="E1450" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="F1450" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="G1450" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H1450" t="inlineStr"/>
+      <c r="I1450" t="inlineStr"/>
+      <c r="J1450" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1450" t="inlineStr"/>
+      <c r="L1450" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1451">
+      <c r="A1451" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B1451" t="inlineStr">
+        <is>
+          <t>Patricia</t>
+        </is>
+      </c>
+      <c r="C1451" t="inlineStr">
+        <is>
+          <t>Ng</t>
+        </is>
+      </c>
+      <c r="D1451" t="inlineStr">
+        <is>
+          <t>1-00010</t>
+        </is>
+      </c>
+      <c r="E1451" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="F1451" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="G1451" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H1451" t="inlineStr"/>
+      <c r="I1451" t="inlineStr"/>
+      <c r="J1451" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1451" t="inlineStr"/>
+      <c r="L1451" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1452">
+      <c r="A1452" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B1452" t="inlineStr">
+        <is>
+          <t>Franklin</t>
+        </is>
+      </c>
+      <c r="C1452" t="inlineStr">
+        <is>
+          <t>Moris</t>
+        </is>
+      </c>
+      <c r="D1452" t="inlineStr">
+        <is>
+          <t>1-00001</t>
+        </is>
+      </c>
+      <c r="E1452" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="F1452" t="inlineStr">
+        <is>
+          <t>08:17</t>
+        </is>
+      </c>
+      <c r="G1452" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H1452" t="inlineStr"/>
+      <c r="I1452" t="inlineStr"/>
+      <c r="J1452" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1452" t="inlineStr"/>
+      <c r="L1452" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1453">
+      <c r="A1453" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B1453" t="inlineStr">
+        <is>
+          <t>Gwen Atasha</t>
+        </is>
+      </c>
+      <c r="C1453" t="inlineStr">
+        <is>
+          <t>Lumagbas</t>
+        </is>
+      </c>
+      <c r="D1453" t="inlineStr">
+        <is>
+          <t>1-00002</t>
+        </is>
+      </c>
+      <c r="E1453" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="F1453" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="G1453" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H1453" t="inlineStr"/>
+      <c r="I1453" t="inlineStr"/>
+      <c r="J1453" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1453" t="inlineStr"/>
+      <c r="L1453" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1454">
+      <c r="A1454" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B1454" t="inlineStr">
+        <is>
+          <t>Maron</t>
+        </is>
+      </c>
+      <c r="C1454" t="inlineStr">
+        <is>
+          <t>Javier</t>
+        </is>
+      </c>
+      <c r="D1454" t="inlineStr">
+        <is>
+          <t>1-00003</t>
+        </is>
+      </c>
+      <c r="E1454" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="F1454" t="inlineStr"/>
+      <c r="G1454" t="inlineStr"/>
+      <c r="H1454" t="inlineStr"/>
+      <c r="I1454" t="inlineStr"/>
+      <c r="J1454" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1454" t="inlineStr"/>
+      <c r="L1454" t="inlineStr">
+        <is>
+          <t>Restday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1455">
+      <c r="A1455" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B1455" t="inlineStr">
+        <is>
+          <t>Elena</t>
+        </is>
+      </c>
+      <c r="C1455" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="D1455" t="inlineStr">
+        <is>
+          <t>1-00004</t>
+        </is>
+      </c>
+      <c r="E1455" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="F1455" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="G1455" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="H1455" t="inlineStr"/>
+      <c r="I1455" t="inlineStr"/>
+      <c r="J1455" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1455" t="inlineStr"/>
+      <c r="L1455" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1456">
+      <c r="A1456" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B1456" t="inlineStr">
+        <is>
+          <t>Miguel</t>
+        </is>
+      </c>
+      <c r="C1456" t="inlineStr">
+        <is>
+          <t>Reyes</t>
+        </is>
+      </c>
+      <c r="D1456" t="inlineStr">
+        <is>
+          <t>1-00005</t>
+        </is>
+      </c>
+      <c r="E1456" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="F1456" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="G1456" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H1456" t="inlineStr"/>
+      <c r="I1456" t="inlineStr"/>
+      <c r="J1456" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1456" t="inlineStr"/>
+      <c r="L1456" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1457">
+      <c r="A1457" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B1457" t="inlineStr">
+        <is>
+          <t>Ana</t>
+        </is>
+      </c>
+      <c r="C1457" t="inlineStr">
+        <is>
+          <t>Cruz</t>
+        </is>
+      </c>
+      <c r="D1457" t="inlineStr">
+        <is>
+          <t>1-00006</t>
+        </is>
+      </c>
+      <c r="E1457" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="F1457" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="G1457" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H1457" t="inlineStr"/>
+      <c r="I1457" t="inlineStr"/>
+      <c r="J1457" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1457" t="inlineStr"/>
+      <c r="L1457" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1458">
+      <c r="A1458" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B1458" t="inlineStr">
+        <is>
+          <t>Roberto</t>
+        </is>
+      </c>
+      <c r="C1458" t="inlineStr">
+        <is>
+          <t>Lim</t>
+        </is>
+      </c>
+      <c r="D1458" t="inlineStr">
+        <is>
+          <t>1-00007</t>
+        </is>
+      </c>
+      <c r="E1458" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="F1458" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="G1458" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H1458" t="inlineStr"/>
+      <c r="I1458" t="inlineStr"/>
+      <c r="J1458" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1458" t="inlineStr"/>
+      <c r="L1458" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1459">
+      <c r="A1459" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B1459" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="C1459" t="inlineStr">
+        <is>
+          <t>Gonzales</t>
+        </is>
+      </c>
+      <c r="D1459" t="inlineStr">
+        <is>
+          <t>1-00008</t>
+        </is>
+      </c>
+      <c r="E1459" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="F1459" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G1459" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="H1459" t="inlineStr"/>
+      <c r="I1459" t="inlineStr"/>
+      <c r="J1459" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1459" t="inlineStr"/>
+      <c r="L1459" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1460">
+      <c r="A1460" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B1460" t="inlineStr">
+        <is>
+          <t>James</t>
+        </is>
+      </c>
+      <c r="C1460" t="inlineStr">
+        <is>
+          <t>Villanueva</t>
+        </is>
+      </c>
+      <c r="D1460" t="inlineStr">
+        <is>
+          <t>1-00009</t>
+        </is>
+      </c>
+      <c r="E1460" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="F1460" t="inlineStr"/>
+      <c r="G1460" t="inlineStr"/>
+      <c r="H1460" t="inlineStr"/>
+      <c r="I1460" t="inlineStr"/>
+      <c r="J1460" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1460" t="inlineStr"/>
+      <c r="L1460" t="inlineStr">
+        <is>
+          <t>Restday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1461">
+      <c r="A1461" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B1461" t="inlineStr">
+        <is>
+          <t>Patricia</t>
+        </is>
+      </c>
+      <c r="C1461" t="inlineStr">
+        <is>
+          <t>Ng</t>
+        </is>
+      </c>
+      <c r="D1461" t="inlineStr">
+        <is>
+          <t>1-00010</t>
+        </is>
+      </c>
+      <c r="E1461" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="F1461" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="G1461" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H1461" t="inlineStr"/>
+      <c r="I1461" t="inlineStr"/>
+      <c r="J1461" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1461" t="inlineStr"/>
+      <c r="L1461" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1462">
+      <c r="A1462" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B1462" t="inlineStr">
+        <is>
+          <t>Franklin</t>
+        </is>
+      </c>
+      <c r="C1462" t="inlineStr">
+        <is>
+          <t>Moris</t>
+        </is>
+      </c>
+      <c r="D1462" t="inlineStr">
+        <is>
+          <t>1-00001</t>
+        </is>
+      </c>
+      <c r="E1462" t="inlineStr">
+        <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="F1462" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="G1462" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H1462" t="inlineStr"/>
+      <c r="I1462" t="inlineStr"/>
+      <c r="J1462" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1462" t="inlineStr"/>
+      <c r="L1462" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1463">
+      <c r="A1463" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B1463" t="inlineStr">
+        <is>
+          <t>Gwen Atasha</t>
+        </is>
+      </c>
+      <c r="C1463" t="inlineStr">
+        <is>
+          <t>Lumagbas</t>
+        </is>
+      </c>
+      <c r="D1463" t="inlineStr">
+        <is>
+          <t>1-00002</t>
+        </is>
+      </c>
+      <c r="E1463" t="inlineStr">
+        <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="F1463" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="G1463" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H1463" t="inlineStr"/>
+      <c r="I1463" t="inlineStr"/>
+      <c r="J1463" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1463" t="inlineStr"/>
+      <c r="L1463" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1464">
+      <c r="A1464" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B1464" t="inlineStr">
+        <is>
+          <t>Maron</t>
+        </is>
+      </c>
+      <c r="C1464" t="inlineStr">
+        <is>
+          <t>Javier</t>
+        </is>
+      </c>
+      <c r="D1464" t="inlineStr">
+        <is>
+          <t>1-00003</t>
+        </is>
+      </c>
+      <c r="E1464" t="inlineStr">
+        <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="F1464" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="G1464" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H1464" t="inlineStr"/>
+      <c r="I1464" t="inlineStr"/>
+      <c r="J1464" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1464" t="inlineStr"/>
+      <c r="L1464" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1465">
+      <c r="A1465" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B1465" t="inlineStr">
+        <is>
+          <t>Elena</t>
+        </is>
+      </c>
+      <c r="C1465" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="D1465" t="inlineStr">
+        <is>
+          <t>1-00004</t>
+        </is>
+      </c>
+      <c r="E1465" t="inlineStr">
+        <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="F1465" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="G1465" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="H1465" t="inlineStr"/>
+      <c r="I1465" t="inlineStr"/>
+      <c r="J1465" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1465" t="inlineStr"/>
+      <c r="L1465" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1466">
+      <c r="A1466" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B1466" t="inlineStr">
+        <is>
+          <t>Miguel</t>
+        </is>
+      </c>
+      <c r="C1466" t="inlineStr">
+        <is>
+          <t>Reyes</t>
+        </is>
+      </c>
+      <c r="D1466" t="inlineStr">
+        <is>
+          <t>1-00005</t>
+        </is>
+      </c>
+      <c r="E1466" t="inlineStr">
+        <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="F1466" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="G1466" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H1466" t="inlineStr"/>
+      <c r="I1466" t="inlineStr"/>
+      <c r="J1466" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1466" t="inlineStr"/>
+      <c r="L1466" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1467">
+      <c r="A1467" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B1467" t="inlineStr">
+        <is>
+          <t>Ana</t>
+        </is>
+      </c>
+      <c r="C1467" t="inlineStr">
+        <is>
+          <t>Cruz</t>
+        </is>
+      </c>
+      <c r="D1467" t="inlineStr">
+        <is>
+          <t>1-00006</t>
+        </is>
+      </c>
+      <c r="E1467" t="inlineStr">
+        <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="F1467" t="inlineStr"/>
+      <c r="G1467" t="inlineStr"/>
+      <c r="H1467" t="inlineStr"/>
+      <c r="I1467" t="inlineStr"/>
+      <c r="J1467" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1467" t="inlineStr"/>
+      <c r="L1467" t="inlineStr">
+        <is>
+          <t>Restday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1468">
+      <c r="A1468" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B1468" t="inlineStr">
+        <is>
+          <t>Roberto</t>
+        </is>
+      </c>
+      <c r="C1468" t="inlineStr">
+        <is>
+          <t>Lim</t>
+        </is>
+      </c>
+      <c r="D1468" t="inlineStr">
+        <is>
+          <t>1-00007</t>
+        </is>
+      </c>
+      <c r="E1468" t="inlineStr">
+        <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="F1468" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="G1468" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H1468" t="inlineStr"/>
+      <c r="I1468" t="inlineStr"/>
+      <c r="J1468" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1468" t="inlineStr"/>
+      <c r="L1468" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1469">
+      <c r="A1469" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B1469" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="C1469" t="inlineStr">
+        <is>
+          <t>Gonzales</t>
+        </is>
+      </c>
+      <c r="D1469" t="inlineStr">
+        <is>
+          <t>1-00008</t>
+        </is>
+      </c>
+      <c r="E1469" t="inlineStr">
+        <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="F1469" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G1469" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="H1469" t="inlineStr"/>
+      <c r="I1469" t="inlineStr"/>
+      <c r="J1469" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1469" t="inlineStr"/>
+      <c r="L1469" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1470">
+      <c r="A1470" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B1470" t="inlineStr">
+        <is>
+          <t>James</t>
+        </is>
+      </c>
+      <c r="C1470" t="inlineStr">
+        <is>
+          <t>Villanueva</t>
+        </is>
+      </c>
+      <c r="D1470" t="inlineStr">
+        <is>
+          <t>1-00009</t>
+        </is>
+      </c>
+      <c r="E1470" t="inlineStr">
+        <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="F1470" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="G1470" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H1470" t="inlineStr"/>
+      <c r="I1470" t="inlineStr"/>
+      <c r="J1470" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1470" t="inlineStr"/>
+      <c r="L1470" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1471">
+      <c r="A1471" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B1471" t="inlineStr">
+        <is>
+          <t>Patricia</t>
+        </is>
+      </c>
+      <c r="C1471" t="inlineStr">
+        <is>
+          <t>Ng</t>
+        </is>
+      </c>
+      <c r="D1471" t="inlineStr">
+        <is>
+          <t>1-00010</t>
+        </is>
+      </c>
+      <c r="E1471" t="inlineStr">
+        <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="F1471" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="G1471" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H1471" t="inlineStr"/>
+      <c r="I1471" t="inlineStr"/>
+      <c r="J1471" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1471" t="inlineStr"/>
+      <c r="L1471" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1472">
+      <c r="A1472" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B1472" t="inlineStr">
+        <is>
+          <t>Franklin</t>
+        </is>
+      </c>
+      <c r="C1472" t="inlineStr">
+        <is>
+          <t>Moris</t>
+        </is>
+      </c>
+      <c r="D1472" t="inlineStr">
+        <is>
+          <t>1-00001</t>
+        </is>
+      </c>
+      <c r="E1472" t="inlineStr">
+        <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="F1472" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="G1472" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H1472" t="inlineStr"/>
+      <c r="I1472" t="inlineStr"/>
+      <c r="J1472" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1472" t="inlineStr"/>
+      <c r="L1472" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1473">
+      <c r="A1473" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B1473" t="inlineStr">
+        <is>
+          <t>Gwen Atasha</t>
+        </is>
+      </c>
+      <c r="C1473" t="inlineStr">
+        <is>
+          <t>Lumagbas</t>
+        </is>
+      </c>
+      <c r="D1473" t="inlineStr">
+        <is>
+          <t>1-00002</t>
+        </is>
+      </c>
+      <c r="E1473" t="inlineStr">
+        <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="F1473" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="G1473" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H1473" t="inlineStr"/>
+      <c r="I1473" t="inlineStr"/>
+      <c r="J1473" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1473" t="inlineStr"/>
+      <c r="L1473" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1474">
+      <c r="A1474" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B1474" t="inlineStr">
+        <is>
+          <t>Maron</t>
+        </is>
+      </c>
+      <c r="C1474" t="inlineStr">
+        <is>
+          <t>Javier</t>
+        </is>
+      </c>
+      <c r="D1474" t="inlineStr">
+        <is>
+          <t>1-00003</t>
+        </is>
+      </c>
+      <c r="E1474" t="inlineStr">
+        <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="F1474" t="inlineStr"/>
+      <c r="G1474" t="inlineStr"/>
+      <c r="H1474" t="inlineStr"/>
+      <c r="I1474" t="inlineStr"/>
+      <c r="J1474" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1474" t="inlineStr"/>
+      <c r="L1474" t="inlineStr">
+        <is>
+          <t>Restday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1475">
+      <c r="A1475" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B1475" t="inlineStr">
+        <is>
+          <t>Elena</t>
+        </is>
+      </c>
+      <c r="C1475" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="D1475" t="inlineStr">
+        <is>
+          <t>1-00004</t>
+        </is>
+      </c>
+      <c r="E1475" t="inlineStr">
+        <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="F1475" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="G1475" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="H1475" t="inlineStr"/>
+      <c r="I1475" t="inlineStr"/>
+      <c r="J1475" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1475" t="inlineStr"/>
+      <c r="L1475" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1476">
+      <c r="A1476" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B1476" t="inlineStr">
+        <is>
+          <t>Miguel</t>
+        </is>
+      </c>
+      <c r="C1476" t="inlineStr">
+        <is>
+          <t>Reyes</t>
+        </is>
+      </c>
+      <c r="D1476" t="inlineStr">
+        <is>
+          <t>1-00005</t>
+        </is>
+      </c>
+      <c r="E1476" t="inlineStr">
+        <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="F1476" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="G1476" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H1476" t="inlineStr"/>
+      <c r="I1476" t="inlineStr"/>
+      <c r="J1476" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1476" t="inlineStr"/>
+      <c r="L1476" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1477">
+      <c r="A1477" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B1477" t="inlineStr">
+        <is>
+          <t>Ana</t>
+        </is>
+      </c>
+      <c r="C1477" t="inlineStr">
+        <is>
+          <t>Cruz</t>
+        </is>
+      </c>
+      <c r="D1477" t="inlineStr">
+        <is>
+          <t>1-00006</t>
+        </is>
+      </c>
+      <c r="E1477" t="inlineStr">
+        <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="F1477" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="G1477" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H1477" t="inlineStr"/>
+      <c r="I1477" t="inlineStr"/>
+      <c r="J1477" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1477" t="inlineStr"/>
+      <c r="L1477" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1478">
+      <c r="A1478" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B1478" t="inlineStr">
+        <is>
+          <t>Roberto</t>
+        </is>
+      </c>
+      <c r="C1478" t="inlineStr">
+        <is>
+          <t>Lim</t>
+        </is>
+      </c>
+      <c r="D1478" t="inlineStr">
+        <is>
+          <t>1-00007</t>
+        </is>
+      </c>
+      <c r="E1478" t="inlineStr">
+        <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="F1478" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="G1478" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H1478" t="inlineStr"/>
+      <c r="I1478" t="inlineStr"/>
+      <c r="J1478" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1478" t="inlineStr"/>
+      <c r="L1478" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1479">
+      <c r="A1479" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B1479" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="C1479" t="inlineStr">
+        <is>
+          <t>Gonzales</t>
+        </is>
+      </c>
+      <c r="D1479" t="inlineStr">
+        <is>
+          <t>1-00008</t>
+        </is>
+      </c>
+      <c r="E1479" t="inlineStr">
+        <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="F1479" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G1479" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="H1479" t="inlineStr"/>
+      <c r="I1479" t="inlineStr"/>
+      <c r="J1479" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1479" t="inlineStr"/>
+      <c r="L1479" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1480">
+      <c r="A1480" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B1480" t="inlineStr">
+        <is>
+          <t>James</t>
+        </is>
+      </c>
+      <c r="C1480" t="inlineStr">
+        <is>
+          <t>Villanueva</t>
+        </is>
+      </c>
+      <c r="D1480" t="inlineStr">
+        <is>
+          <t>1-00009</t>
+        </is>
+      </c>
+      <c r="E1480" t="inlineStr">
+        <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="F1480" t="inlineStr"/>
+      <c r="G1480" t="inlineStr"/>
+      <c r="H1480" t="inlineStr"/>
+      <c r="I1480" t="inlineStr"/>
+      <c r="J1480" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1480" t="inlineStr"/>
+      <c r="L1480" t="inlineStr">
+        <is>
+          <t>Restday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1481">
+      <c r="A1481" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B1481" t="inlineStr">
+        <is>
+          <t>Patricia</t>
+        </is>
+      </c>
+      <c r="C1481" t="inlineStr">
+        <is>
+          <t>Ng</t>
+        </is>
+      </c>
+      <c r="D1481" t="inlineStr">
+        <is>
+          <t>1-00010</t>
+        </is>
+      </c>
+      <c r="E1481" t="inlineStr">
+        <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="F1481" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="G1481" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H1481" t="inlineStr"/>
+      <c r="I1481" t="inlineStr"/>
+      <c r="J1481" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1481" t="inlineStr"/>
+      <c r="L1481" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1482">
+      <c r="A1482" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B1482" t="inlineStr">
+        <is>
+          <t>Franklin</t>
+        </is>
+      </c>
+      <c r="C1482" t="inlineStr">
+        <is>
+          <t>Moris</t>
+        </is>
+      </c>
+      <c r="D1482" t="inlineStr">
+        <is>
+          <t>1-00001</t>
+        </is>
+      </c>
+      <c r="E1482" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="F1482" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="G1482" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H1482" t="inlineStr"/>
+      <c r="I1482" t="inlineStr"/>
+      <c r="J1482" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1482" t="inlineStr"/>
+      <c r="L1482" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1483">
+      <c r="A1483" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B1483" t="inlineStr">
+        <is>
+          <t>Gwen Atasha</t>
+        </is>
+      </c>
+      <c r="C1483" t="inlineStr">
+        <is>
+          <t>Lumagbas</t>
+        </is>
+      </c>
+      <c r="D1483" t="inlineStr">
+        <is>
+          <t>1-00002</t>
+        </is>
+      </c>
+      <c r="E1483" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="F1483" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="G1483" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H1483" t="inlineStr"/>
+      <c r="I1483" t="inlineStr"/>
+      <c r="J1483" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1483" t="inlineStr"/>
+      <c r="L1483" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1484">
+      <c r="A1484" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B1484" t="inlineStr">
+        <is>
+          <t>Maron</t>
+        </is>
+      </c>
+      <c r="C1484" t="inlineStr">
+        <is>
+          <t>Javier</t>
+        </is>
+      </c>
+      <c r="D1484" t="inlineStr">
+        <is>
+          <t>1-00003</t>
+        </is>
+      </c>
+      <c r="E1484" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="F1484" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="G1484" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H1484" t="inlineStr"/>
+      <c r="I1484" t="inlineStr"/>
+      <c r="J1484" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1484" t="inlineStr"/>
+      <c r="L1484" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1485">
+      <c r="A1485" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B1485" t="inlineStr">
+        <is>
+          <t>Elena</t>
+        </is>
+      </c>
+      <c r="C1485" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="D1485" t="inlineStr">
+        <is>
+          <t>1-00004</t>
+        </is>
+      </c>
+      <c r="E1485" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="F1485" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="G1485" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="H1485" t="inlineStr"/>
+      <c r="I1485" t="inlineStr"/>
+      <c r="J1485" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1485" t="inlineStr"/>
+      <c r="L1485" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1486">
+      <c r="A1486" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B1486" t="inlineStr">
+        <is>
+          <t>Miguel</t>
+        </is>
+      </c>
+      <c r="C1486" t="inlineStr">
+        <is>
+          <t>Reyes</t>
+        </is>
+      </c>
+      <c r="D1486" t="inlineStr">
+        <is>
+          <t>1-00005</t>
+        </is>
+      </c>
+      <c r="E1486" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="F1486" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="G1486" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H1486" t="inlineStr"/>
+      <c r="I1486" t="inlineStr"/>
+      <c r="J1486" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1486" t="inlineStr"/>
+      <c r="L1486" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1487">
+      <c r="A1487" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B1487" t="inlineStr">
+        <is>
+          <t>Ana</t>
+        </is>
+      </c>
+      <c r="C1487" t="inlineStr">
+        <is>
+          <t>Cruz</t>
+        </is>
+      </c>
+      <c r="D1487" t="inlineStr">
+        <is>
+          <t>1-00006</t>
+        </is>
+      </c>
+      <c r="E1487" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="F1487" t="inlineStr"/>
+      <c r="G1487" t="inlineStr"/>
+      <c r="H1487" t="inlineStr"/>
+      <c r="I1487" t="inlineStr"/>
+      <c r="J1487" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1487" t="inlineStr"/>
+      <c r="L1487" t="inlineStr">
+        <is>
+          <t>Restday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1488">
+      <c r="A1488" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B1488" t="inlineStr">
+        <is>
+          <t>Roberto</t>
+        </is>
+      </c>
+      <c r="C1488" t="inlineStr">
+        <is>
+          <t>Lim</t>
+        </is>
+      </c>
+      <c r="D1488" t="inlineStr">
+        <is>
+          <t>1-00007</t>
+        </is>
+      </c>
+      <c r="E1488" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="F1488" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="G1488" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H1488" t="inlineStr"/>
+      <c r="I1488" t="inlineStr"/>
+      <c r="J1488" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1488" t="inlineStr"/>
+      <c r="L1488" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1489">
+      <c r="A1489" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B1489" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="C1489" t="inlineStr">
+        <is>
+          <t>Gonzales</t>
+        </is>
+      </c>
+      <c r="D1489" t="inlineStr">
+        <is>
+          <t>1-00008</t>
+        </is>
+      </c>
+      <c r="E1489" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="F1489" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G1489" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="H1489" t="inlineStr"/>
+      <c r="I1489" t="inlineStr"/>
+      <c r="J1489" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1489" t="inlineStr"/>
+      <c r="L1489" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1490">
+      <c r="A1490" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B1490" t="inlineStr">
+        <is>
+          <t>James</t>
+        </is>
+      </c>
+      <c r="C1490" t="inlineStr">
+        <is>
+          <t>Villanueva</t>
+        </is>
+      </c>
+      <c r="D1490" t="inlineStr">
+        <is>
+          <t>1-00009</t>
+        </is>
+      </c>
+      <c r="E1490" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="F1490" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="G1490" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H1490" t="inlineStr"/>
+      <c r="I1490" t="inlineStr"/>
+      <c r="J1490" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1490" t="inlineStr"/>
+      <c r="L1490" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1491">
+      <c r="A1491" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B1491" t="inlineStr">
+        <is>
+          <t>Patricia</t>
+        </is>
+      </c>
+      <c r="C1491" t="inlineStr">
+        <is>
+          <t>Ng</t>
+        </is>
+      </c>
+      <c r="D1491" t="inlineStr">
+        <is>
+          <t>1-00010</t>
+        </is>
+      </c>
+      <c r="E1491" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="F1491" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="G1491" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H1491" t="inlineStr"/>
+      <c r="I1491" t="inlineStr"/>
+      <c r="J1491" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1491" t="inlineStr"/>
+      <c r="L1491" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1492">
+      <c r="A1492" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B1492" t="inlineStr">
+        <is>
+          <t>Franklin</t>
+        </is>
+      </c>
+      <c r="C1492" t="inlineStr">
+        <is>
+          <t>Moris</t>
+        </is>
+      </c>
+      <c r="D1492" t="inlineStr">
+        <is>
+          <t>1-00001</t>
+        </is>
+      </c>
+      <c r="E1492" t="inlineStr">
+        <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="F1492" t="inlineStr"/>
+      <c r="G1492" t="inlineStr"/>
+      <c r="H1492" t="inlineStr"/>
+      <c r="I1492" t="inlineStr"/>
+      <c r="J1492" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1492" t="inlineStr"/>
+      <c r="L1492" t="inlineStr">
+        <is>
+          <t>Restday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1493">
+      <c r="A1493" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B1493" t="inlineStr">
+        <is>
+          <t>Gwen Atasha</t>
+        </is>
+      </c>
+      <c r="C1493" t="inlineStr">
+        <is>
+          <t>Lumagbas</t>
+        </is>
+      </c>
+      <c r="D1493" t="inlineStr">
+        <is>
+          <t>1-00002</t>
+        </is>
+      </c>
+      <c r="E1493" t="inlineStr">
+        <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="F1493" t="inlineStr"/>
+      <c r="G1493" t="inlineStr"/>
+      <c r="H1493" t="inlineStr"/>
+      <c r="I1493" t="inlineStr"/>
+      <c r="J1493" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1493" t="inlineStr"/>
+      <c r="L1493" t="inlineStr">
+        <is>
+          <t>Restday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1494">
+      <c r="A1494" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B1494" t="inlineStr">
+        <is>
+          <t>Maron</t>
+        </is>
+      </c>
+      <c r="C1494" t="inlineStr">
+        <is>
+          <t>Javier</t>
+        </is>
+      </c>
+      <c r="D1494" t="inlineStr">
+        <is>
+          <t>1-00003</t>
+        </is>
+      </c>
+      <c r="E1494" t="inlineStr">
+        <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="F1494" t="inlineStr"/>
+      <c r="G1494" t="inlineStr"/>
+      <c r="H1494" t="inlineStr"/>
+      <c r="I1494" t="inlineStr"/>
+      <c r="J1494" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1494" t="inlineStr"/>
+      <c r="L1494" t="inlineStr">
+        <is>
+          <t>Restday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1495">
+      <c r="A1495" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B1495" t="inlineStr">
+        <is>
+          <t>Elena</t>
+        </is>
+      </c>
+      <c r="C1495" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="D1495" t="inlineStr">
+        <is>
+          <t>1-00004</t>
+        </is>
+      </c>
+      <c r="E1495" t="inlineStr">
+        <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="F1495" t="inlineStr"/>
+      <c r="G1495" t="inlineStr"/>
+      <c r="H1495" t="inlineStr"/>
+      <c r="I1495" t="inlineStr"/>
+      <c r="J1495" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1495" t="inlineStr"/>
+      <c r="L1495" t="inlineStr">
+        <is>
+          <t>Restday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1496">
+      <c r="A1496" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B1496" t="inlineStr">
+        <is>
+          <t>Miguel</t>
+        </is>
+      </c>
+      <c r="C1496" t="inlineStr">
+        <is>
+          <t>Reyes</t>
+        </is>
+      </c>
+      <c r="D1496" t="inlineStr">
+        <is>
+          <t>1-00005</t>
+        </is>
+      </c>
+      <c r="E1496" t="inlineStr">
+        <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="F1496" t="inlineStr"/>
+      <c r="G1496" t="inlineStr"/>
+      <c r="H1496" t="inlineStr"/>
+      <c r="I1496" t="inlineStr"/>
+      <c r="J1496" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1496" t="inlineStr"/>
+      <c r="L1496" t="inlineStr">
+        <is>
+          <t>Restday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1497">
+      <c r="A1497" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B1497" t="inlineStr">
+        <is>
+          <t>Ana</t>
+        </is>
+      </c>
+      <c r="C1497" t="inlineStr">
+        <is>
+          <t>Cruz</t>
+        </is>
+      </c>
+      <c r="D1497" t="inlineStr">
+        <is>
+          <t>1-00006</t>
+        </is>
+      </c>
+      <c r="E1497" t="inlineStr">
+        <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="F1497" t="inlineStr"/>
+      <c r="G1497" t="inlineStr"/>
+      <c r="H1497" t="inlineStr"/>
+      <c r="I1497" t="inlineStr"/>
+      <c r="J1497" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1497" t="inlineStr"/>
+      <c r="L1497" t="inlineStr">
+        <is>
+          <t>Restday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1498">
+      <c r="A1498" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B1498" t="inlineStr">
+        <is>
+          <t>Roberto</t>
+        </is>
+      </c>
+      <c r="C1498" t="inlineStr">
+        <is>
+          <t>Lim</t>
+        </is>
+      </c>
+      <c r="D1498" t="inlineStr">
+        <is>
+          <t>1-00007</t>
+        </is>
+      </c>
+      <c r="E1498" t="inlineStr">
+        <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="F1498" t="inlineStr"/>
+      <c r="G1498" t="inlineStr"/>
+      <c r="H1498" t="inlineStr"/>
+      <c r="I1498" t="inlineStr"/>
+      <c r="J1498" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1498" t="inlineStr"/>
+      <c r="L1498" t="inlineStr">
+        <is>
+          <t>Restday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1499">
+      <c r="A1499" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B1499" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="C1499" t="inlineStr">
+        <is>
+          <t>Gonzales</t>
+        </is>
+      </c>
+      <c r="D1499" t="inlineStr">
+        <is>
+          <t>1-00008</t>
+        </is>
+      </c>
+      <c r="E1499" t="inlineStr">
+        <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="F1499" t="inlineStr"/>
+      <c r="G1499" t="inlineStr"/>
+      <c r="H1499" t="inlineStr"/>
+      <c r="I1499" t="inlineStr"/>
+      <c r="J1499" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1499" t="inlineStr"/>
+      <c r="L1499" t="inlineStr">
+        <is>
+          <t>Restday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1500">
+      <c r="A1500" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B1500" t="inlineStr">
+        <is>
+          <t>James</t>
+        </is>
+      </c>
+      <c r="C1500" t="inlineStr">
+        <is>
+          <t>Villanueva</t>
+        </is>
+      </c>
+      <c r="D1500" t="inlineStr">
+        <is>
+          <t>1-00009</t>
+        </is>
+      </c>
+      <c r="E1500" t="inlineStr">
+        <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="F1500" t="inlineStr"/>
+      <c r="G1500" t="inlineStr"/>
+      <c r="H1500" t="inlineStr"/>
+      <c r="I1500" t="inlineStr"/>
+      <c r="J1500" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1500" t="inlineStr"/>
+      <c r="L1500" t="inlineStr">
+        <is>
+          <t>Restday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1501">
+      <c r="A1501" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B1501" t="inlineStr">
+        <is>
+          <t>Patricia</t>
+        </is>
+      </c>
+      <c r="C1501" t="inlineStr">
+        <is>
+          <t>Ng</t>
+        </is>
+      </c>
+      <c r="D1501" t="inlineStr">
+        <is>
+          <t>1-00010</t>
+        </is>
+      </c>
+      <c r="E1501" t="inlineStr">
+        <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="F1501" t="inlineStr"/>
+      <c r="G1501" t="inlineStr"/>
+      <c r="H1501" t="inlineStr"/>
+      <c r="I1501" t="inlineStr"/>
+      <c r="J1501" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1501" t="inlineStr"/>
+      <c r="L1501" t="inlineStr">
+        <is>
+          <t>Restday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1502">
+      <c r="A1502" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B1502" t="inlineStr">
+        <is>
+          <t>Franklin</t>
+        </is>
+      </c>
+      <c r="C1502" t="inlineStr">
+        <is>
+          <t>Moris</t>
+        </is>
+      </c>
+      <c r="D1502" t="inlineStr">
+        <is>
+          <t>1-00001</t>
+        </is>
+      </c>
+      <c r="E1502" t="inlineStr">
+        <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="F1502" t="inlineStr"/>
+      <c r="G1502" t="inlineStr"/>
+      <c r="H1502" t="inlineStr"/>
+      <c r="I1502" t="inlineStr"/>
+      <c r="J1502" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1502" t="inlineStr"/>
+      <c r="L1502" t="inlineStr">
+        <is>
+          <t>Restday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1503">
+      <c r="A1503" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B1503" t="inlineStr">
+        <is>
+          <t>Gwen Atasha</t>
+        </is>
+      </c>
+      <c r="C1503" t="inlineStr">
+        <is>
+          <t>Lumagbas</t>
+        </is>
+      </c>
+      <c r="D1503" t="inlineStr">
+        <is>
+          <t>1-00002</t>
+        </is>
+      </c>
+      <c r="E1503" t="inlineStr">
+        <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="F1503" t="inlineStr"/>
+      <c r="G1503" t="inlineStr"/>
+      <c r="H1503" t="inlineStr"/>
+      <c r="I1503" t="inlineStr"/>
+      <c r="J1503" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1503" t="inlineStr"/>
+      <c r="L1503" t="inlineStr">
+        <is>
+          <t>Restday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1504">
+      <c r="A1504" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B1504" t="inlineStr">
+        <is>
+          <t>Maron</t>
+        </is>
+      </c>
+      <c r="C1504" t="inlineStr">
+        <is>
+          <t>Javier</t>
+        </is>
+      </c>
+      <c r="D1504" t="inlineStr">
+        <is>
+          <t>1-00003</t>
+        </is>
+      </c>
+      <c r="E1504" t="inlineStr">
+        <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="F1504" t="inlineStr"/>
+      <c r="G1504" t="inlineStr"/>
+      <c r="H1504" t="inlineStr"/>
+      <c r="I1504" t="inlineStr"/>
+      <c r="J1504" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1504" t="inlineStr"/>
+      <c r="L1504" t="inlineStr">
+        <is>
+          <t>Restday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1505">
+      <c r="A1505" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B1505" t="inlineStr">
+        <is>
+          <t>Elena</t>
+        </is>
+      </c>
+      <c r="C1505" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="D1505" t="inlineStr">
+        <is>
+          <t>1-00004</t>
+        </is>
+      </c>
+      <c r="E1505" t="inlineStr">
+        <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="F1505" t="inlineStr"/>
+      <c r="G1505" t="inlineStr"/>
+      <c r="H1505" t="inlineStr"/>
+      <c r="I1505" t="inlineStr"/>
+      <c r="J1505" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1505" t="inlineStr"/>
+      <c r="L1505" t="inlineStr">
+        <is>
+          <t>Restday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1506">
+      <c r="A1506" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B1506" t="inlineStr">
+        <is>
+          <t>Miguel</t>
+        </is>
+      </c>
+      <c r="C1506" t="inlineStr">
+        <is>
+          <t>Reyes</t>
+        </is>
+      </c>
+      <c r="D1506" t="inlineStr">
+        <is>
+          <t>1-00005</t>
+        </is>
+      </c>
+      <c r="E1506" t="inlineStr">
+        <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="F1506" t="inlineStr"/>
+      <c r="G1506" t="inlineStr"/>
+      <c r="H1506" t="inlineStr"/>
+      <c r="I1506" t="inlineStr"/>
+      <c r="J1506" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1506" t="inlineStr"/>
+      <c r="L1506" t="inlineStr">
+        <is>
+          <t>Restday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1507">
+      <c r="A1507" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B1507" t="inlineStr">
+        <is>
+          <t>Ana</t>
+        </is>
+      </c>
+      <c r="C1507" t="inlineStr">
+        <is>
+          <t>Cruz</t>
+        </is>
+      </c>
+      <c r="D1507" t="inlineStr">
+        <is>
+          <t>1-00006</t>
+        </is>
+      </c>
+      <c r="E1507" t="inlineStr">
+        <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="F1507" t="inlineStr"/>
+      <c r="G1507" t="inlineStr"/>
+      <c r="H1507" t="inlineStr"/>
+      <c r="I1507" t="inlineStr"/>
+      <c r="J1507" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1507" t="inlineStr"/>
+      <c r="L1507" t="inlineStr">
+        <is>
+          <t>Restday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1508">
+      <c r="A1508" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B1508" t="inlineStr">
+        <is>
+          <t>Roberto</t>
+        </is>
+      </c>
+      <c r="C1508" t="inlineStr">
+        <is>
+          <t>Lim</t>
+        </is>
+      </c>
+      <c r="D1508" t="inlineStr">
+        <is>
+          <t>1-00007</t>
+        </is>
+      </c>
+      <c r="E1508" t="inlineStr">
+        <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="F1508" t="inlineStr"/>
+      <c r="G1508" t="inlineStr"/>
+      <c r="H1508" t="inlineStr"/>
+      <c r="I1508" t="inlineStr"/>
+      <c r="J1508" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1508" t="inlineStr"/>
+      <c r="L1508" t="inlineStr">
+        <is>
+          <t>Restday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1509">
+      <c r="A1509" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B1509" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="C1509" t="inlineStr">
+        <is>
+          <t>Gonzales</t>
+        </is>
+      </c>
+      <c r="D1509" t="inlineStr">
+        <is>
+          <t>1-00008</t>
+        </is>
+      </c>
+      <c r="E1509" t="inlineStr">
+        <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="F1509" t="inlineStr"/>
+      <c r="G1509" t="inlineStr"/>
+      <c r="H1509" t="inlineStr"/>
+      <c r="I1509" t="inlineStr"/>
+      <c r="J1509" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1509" t="inlineStr"/>
+      <c r="L1509" t="inlineStr">
+        <is>
+          <t>Restday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1510">
+      <c r="A1510" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B1510" t="inlineStr">
+        <is>
+          <t>James</t>
+        </is>
+      </c>
+      <c r="C1510" t="inlineStr">
+        <is>
+          <t>Villanueva</t>
+        </is>
+      </c>
+      <c r="D1510" t="inlineStr">
+        <is>
+          <t>1-00009</t>
+        </is>
+      </c>
+      <c r="E1510" t="inlineStr">
+        <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="F1510" t="inlineStr"/>
+      <c r="G1510" t="inlineStr"/>
+      <c r="H1510" t="inlineStr"/>
+      <c r="I1510" t="inlineStr"/>
+      <c r="J1510" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1510" t="inlineStr"/>
+      <c r="L1510" t="inlineStr">
+        <is>
+          <t>Restday</t>
+        </is>
+      </c>
+    </row>
+    <row r="1511">
+      <c r="A1511" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B1511" t="inlineStr">
+        <is>
+          <t>Patricia</t>
+        </is>
+      </c>
+      <c r="C1511" t="inlineStr">
+        <is>
+          <t>Ng</t>
+        </is>
+      </c>
+      <c r="D1511" t="inlineStr">
+        <is>
+          <t>1-00010</t>
+        </is>
+      </c>
+      <c r="E1511" t="inlineStr">
+        <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="F1511" t="inlineStr"/>
+      <c r="G1511" t="inlineStr"/>
+      <c r="H1511" t="inlineStr"/>
+      <c r="I1511" t="inlineStr"/>
+      <c r="J1511" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K1511" t="inlineStr"/>
+      <c r="L1511" t="inlineStr">
+        <is>
+          <t>Restday</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
